--- a/order_generation/PO_excel/ST1122-5.xlsx
+++ b/order_generation/PO_excel/ST1122-5.xlsx
@@ -184,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -254,13 +254,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -733,7 +736,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="86.25" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>宁波品秀美容科技有限公司
 宁波高新区江南路1528号高新科技广场2号楼10楼
@@ -741,7 +744,7 @@
 sales@hair-brushes.com    lucky@jsiu.com</t>
         </is>
       </c>
-      <c r="H1" s="28" t="n"/>
+      <c r="H1" s="26" t="n"/>
     </row>
     <row r="2" ht="31.5" customHeight="1">
       <c r="A2" s="27" t="inlineStr">
@@ -863,28 +866,28 @@
       <c r="H6" s="20" t="n"/>
     </row>
     <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>ST1122-5</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n"/>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>爪形木柄猪鬃梳，棕色染头，包装方式：散货</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="29" t="n">
         <v>0.6</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="29">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>散货</t>
         </is>
@@ -892,23 +895,23 @@
       <c r="H7" s="20" t="n"/>
     </row>
     <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="19" t="n"/>
-      <c r="B8" s="19" t="n"/>
-      <c r="C8" s="19" t="n"/>
-      <c r="D8" s="19" t="n"/>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="19" t="n"/>
-      <c r="G8" s="19" t="n"/>
+      <c r="A8" s="29" t="n"/>
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
       <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A9" s="19" t="n"/>
-      <c r="B9" s="19" t="n"/>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="19" t="n"/>
+      <c r="A9" s="29" t="n"/>
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="29" t="n"/>
       <c r="H9" s="20" t="n"/>
     </row>
     <row r="10" ht="17.25" customFormat="1" customHeight="1" s="3">

--- a/order_generation/PO_excel/ST1122-5.xlsx
+++ b/order_generation/PO_excel/ST1122-5.xlsx
@@ -800,7 +800,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>2025年10月09日</t>
+          <t>2025年10月21日</t>
         </is>
       </c>
       <c r="H4" s="16" t="n"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>李万祥</t>
+          <t>多多</t>
         </is>
       </c>
       <c r="C5" s="16" t="n"/>
@@ -992,7 +992,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>2025年10月24日</t>
+          <t>2025年11月05日</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>
